--- a/results/Int Task Remove ACC -0.7/Rando_4_permute.xlsx
+++ b/results/Int Task Remove ACC -0.7/Rando_4_permute.xlsx
@@ -440,107 +440,107 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7084539885207709</v>
+        <v>0.7143725720113587</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7056071214929442</v>
+        <v>0.7083161719278632</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7074283318693604</v>
+        <v>0.7105520578976788</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7048544712816138</v>
+        <v>0.7124408631976811</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7045749855353869</v>
+        <v>0.7217717645146965</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6979011250877333</v>
+        <v>0.7184517330217662</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7012705394004856</v>
+        <v>0.71151659893165</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7015500251467125</v>
+        <v>0.71151659893165</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7082914805179523</v>
+        <v>0.7045567734316227</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7088686641141704</v>
+        <v>0.7186025082269676</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7094185295547422</v>
+        <v>0.7185687107651746</v>
       </c>
     </row>
     <row r="13">
@@ -550,777 +550,777 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7212336318717421</v>
+        <v>0.7190691933859243</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7198453091924893</v>
+        <v>0.7132857997425088</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7196152062660844</v>
+        <v>0.6954428413123361</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7186935687457885</v>
+        <v>0.6961305233458156</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7173299374764468</v>
+        <v>0.6963917969882785</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7196334183698486</v>
+        <v>0.6947577860245919</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7186597712839954</v>
+        <v>0.7127630773412009</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7222501824712704</v>
+        <v>0.7148455613600799</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7269065270778959</v>
+        <v>0.7178678950030191</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7252725161142095</v>
+        <v>0.7078610444501416</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7207175638929633</v>
+        <v>0.7067431014652338</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7029292417740831</v>
+        <v>0.6972223739897536</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7055368998236228</v>
+        <v>0.6995505462930663</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7068238301174961</v>
+        <v>0.6859389250095613</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7007427386240896</v>
+        <v>0.6848209820246536</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6960279051457599</v>
+        <v>0.6978892171737336</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6939272090231168</v>
+        <v>0.6985157835897737</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7171101664166004</v>
+        <v>0.6974745415803343</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.715312421635419</v>
+        <v>0.6882059816954348</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.715346219097212</v>
+        <v>0.6817205464751874</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.715346219097212</v>
+        <v>0.6898165270638866</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7193175084160933</v>
+        <v>0.6924917800370126</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7155983866877927</v>
+        <v>0.6924917800370126</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7155983866877927</v>
+        <v>0.6954062419884255</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7098825879679636</v>
+        <v>0.6967231171836803</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7072138143009845</v>
+        <v>0.6886297633407162</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6972017102566366</v>
+        <v>0.6907082196828012</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6713914817787903</v>
+        <v>0.6846362342412767</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6456152258791192</v>
+        <v>0.6891691217983471</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6413280266064827</v>
+        <v>0.6943259490257225</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6325249260658634</v>
+        <v>0.6965865264054492</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6228572759455935</v>
+        <v>0.7020137333271692</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6221202110922919</v>
+        <v>0.7017342475809423</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6191628456272038</v>
+        <v>0.7017342475809423</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6081588823932385</v>
+        <v>0.7053519769238636</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6028745704395141</v>
+        <v>0.7069430843738749</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6055069198989649</v>
+        <v>0.6978175945733535</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6046164530947267</v>
+        <v>0.695845608991736</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6241998932490533</v>
+        <v>0.6832011554879373</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6122014440797354</v>
+        <v>0.6837301820790097</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6131659851137066</v>
+        <v>0.6840096678252366</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5892265249484807</v>
+        <v>0.680529755075223</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5609531094365314</v>
+        <v>0.6808950478488003</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5609531094365314</v>
+        <v>0.6620161009006587</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5390674142034796</v>
+        <v>0.6613804284327365</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5390674142034796</v>
+        <v>0.648787984494495</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.532648348092142</v>
+        <v>0.6502932849171559</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5224751369760343</v>
+        <v>0.604980169820863</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5228222176458475</v>
+        <v>0.6062424087048253</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4896516725015445</v>
+        <v>0.6162025031836158</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4882334049209104</v>
+        <v>0.6162025031836158</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4773282073265893</v>
+        <v>0.6215556358756029</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4773282073265893</v>
+        <v>0.6241879853350537</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.477714338949666</v>
+        <v>0.624264686310522</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4731593867284197</v>
+        <v>0.5965617999722616</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5022125954909633</v>
+        <v>0.5902935090661253</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5081064875716401</v>
+        <v>0.5868785644939627</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5090645492994644</v>
+        <v>0.5860518400528991</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5131333784433134</v>
+        <v>0.5901518399128061</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5091841537886079</v>
+        <v>0.5913373778213</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5117371755268552</v>
+        <v>0.5913373778213</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4979019306230921</v>
+        <v>0.5830204003580779</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4973429591306382</v>
+        <v>0.5817334700642047</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.499950617180178</v>
+        <v>0.5647147844457426</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.500263900388198</v>
+        <v>0.5655532416844236</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.500263900388198</v>
+        <v>0.5632679728947858</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.500263900388198</v>
+        <v>0.5662227116141387</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5000520095655573</v>
+        <v>0.5552369604839377</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4998401187429165</v>
+        <v>0.5533078784159953</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5004666851589566</v>
+        <v>0.5375111549135556</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5012284414221692</v>
+        <v>0.5180513469251664</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4999662025382069</v>
+        <v>0.511981813112995</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4989587579905605</v>
+        <v>0.4762468636655922</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4989587579905605</v>
+        <v>0.4779328841948359</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4996282279202758</v>
+        <v>0.4810772739562713</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4960131253230897</v>
+        <v>0.4810772739562713</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4967410841245091</v>
+        <v>0.4780705256713612</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4992044462749943</v>
+        <v>0.4889132067171842</v>
       </c>
     </row>
   </sheetData>
